--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -1,18 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A0D054D-FA33-465C-820D-D3BA9CD9623A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\Glowi\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FC7DE3-7767-4DDA-B767-8005F2C98474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BACKLOG" sheetId="1" r:id="rId1"/>
     <sheet name="INSTRUÇÕES" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BACKLOG!$A$4:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BACKLOG!$A$4:$H$16</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -35,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="127">
   <si>
     <t>BACKLOG DO PRODUTO — Todas as Ondas até o MVP</t>
   </si>
@@ -91,90 +96,39 @@
     <t>Backend</t>
   </si>
   <si>
-    <t>Criar model e endpoint REST de cadastro de prestador (nome, categoria, contato)</t>
-  </si>
-  <si>
-    <t>[resp]</t>
-  </si>
-  <si>
-    <t>#1</t>
-  </si>
-  <si>
     <t>T02</t>
   </si>
   <si>
     <t>Frontend</t>
   </si>
   <si>
-    <t>Desenvolver formulário de cadastro com validação (frontend)</t>
-  </si>
-  <si>
-    <t>#2</t>
-  </si>
-  <si>
     <t>T03</t>
   </si>
   <si>
-    <t>Criar tela de perfil público do prestador</t>
-  </si>
-  <si>
-    <t>#3</t>
-  </si>
-  <si>
     <t>T04</t>
   </si>
   <si>
     <t>F02</t>
   </si>
   <si>
-    <t>Implementar endpoint de busca por categoria e raio de distância</t>
-  </si>
-  <si>
-    <t>#4</t>
-  </si>
-  <si>
     <t>T05</t>
   </si>
   <si>
-    <t>Integrar mapa (OpenStreetMap) na tela de busca → subdividida em T05a/T05b/T05c</t>
-  </si>
-  <si>
-    <t>#5</t>
-  </si>
-  <si>
     <t>T06</t>
   </si>
   <si>
     <t>F03</t>
   </si>
   <si>
-    <t>Criar endpoint REST de solicitação de orçamento</t>
-  </si>
-  <si>
-    <t>#6</t>
-  </si>
-  <si>
     <t>T07</t>
   </si>
   <si>
-    <t>Tela de solicitação e confirmação de orçamento</t>
-  </si>
-  <si>
-    <t>#7</t>
-  </si>
-  <si>
     <t>T08</t>
   </si>
   <si>
     <t>DevOps</t>
   </si>
   <si>
-    <t>Configurar envio de notificação por e-mail ao prestador</t>
-  </si>
-  <si>
-    <t>#8</t>
-  </si>
-  <si>
     <t>T09</t>
   </si>
   <si>
@@ -184,36 +138,21 @@
     <t>F04</t>
   </si>
   <si>
-    <t>Implementar sistema de avaliação de prestadores (1–5 estrelas)</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
-    <t>--</t>
-  </si>
-  <si>
     <t>T10</t>
   </si>
   <si>
-    <t>Tela de avaliação e listagem de avaliações</t>
-  </si>
-  <si>
     <t>T11</t>
   </si>
   <si>
     <t>F05</t>
   </si>
   <si>
-    <t>Implementar histórico de orçamentos por usuário</t>
-  </si>
-  <si>
     <t>T12</t>
   </si>
   <si>
-    <t>Tela de histórico com filtro por status</t>
-  </si>
-  <si>
     <t>P</t>
   </si>
   <si>
@@ -226,21 +165,9 @@
     <t>F06</t>
   </si>
   <si>
-    <t>[Tipo]</t>
-  </si>
-  <si>
-    <t>[Descreva a tarefa da Onda 3]</t>
-  </si>
-  <si>
-    <t>[Est]</t>
-  </si>
-  <si>
     <t>T14</t>
   </si>
   <si>
-    <t>↓ Adicione linhas conforme necessário — siga o padrão de ID (T15, T16, …)</t>
-  </si>
-  <si>
     <t>LEGENDA DE CORES</t>
   </si>
   <si>
@@ -320,13 +247,187 @@
   </si>
   <si>
     <t>A coluna 'Issue #' é o elo entre esta planilha e o Kanban. O professor verificará se cada Issue do board tem uma linha correspondente no BACKLOG.xlsx com o número preenchido.</t>
+  </si>
+  <si>
+    <t>Configurar projeto ASP.NET Core MVC com Identity, banco PostgreSQL no Supabase e migrations (concluída)</t>
+  </si>
+  <si>
+    <t>Luisa</t>
+  </si>
+  <si>
+    <t>Cadastro com nome e tipo de usuário (roles Cliente e Profissional), com validação da role no servidor</t>
+  </si>
+  <si>
+    <t>Telas de cadastro e login em português, com escolha "Sou cliente / Sou profissional" e menu por tipo de usuário</t>
+  </si>
+  <si>
+    <t>Criar model Servico (nome, duração, preço) e CRUD restrito à profissional logada</t>
+  </si>
+  <si>
+    <t>Tela "Meus serviços" da profissional e listagem de profissionais com serviços e preços para a cliente</t>
+  </si>
+  <si>
+    <t>Criar model Disponibilidade e CRUD dos horários de atendimento por dia da semana</t>
+  </si>
+  <si>
+    <t>Calcular horários livres e criar agendamento, com constraint no banco que impede horários sobrepostos</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Tela de agendar: escolher profissional, serviço, data e horário livre, com tela de confirmação</t>
+  </si>
+  <si>
+    <t>Tela "Meus agendamentos" para cliente e profissional, com cancelamento</t>
+  </si>
+  <si>
+    <t>Documentação</t>
+  </si>
+  <si>
+    <t>Definir regras de negócio do agendamento (intervalo entre horários, antecedência mínima, cancelamento)</t>
+  </si>
+  <si>
+    <t>Transformar o site em PWA (manifest, ícone e service worker)</t>
+  </si>
+  <si>
+    <t>T15</t>
+  </si>
+  <si>
+    <t>T16</t>
+  </si>
+  <si>
+    <t>Agenda da profissional em visão diária e semanal, com os agendamentos do período</t>
+  </si>
+  <si>
+    <t>T17</t>
+  </si>
+  <si>
+    <t>Calendário de horários disponíveis para a cliente, por profissional e serviço</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>T19</t>
+  </si>
+  <si>
+    <t>Lista de pedidos pendentes com botões confirmar e recusar, e status visível para a cliente</t>
+  </si>
+  <si>
+    <t>T20</t>
+  </si>
+  <si>
+    <t>T21</t>
+  </si>
+  <si>
+    <t>Criar model Favorito (cliente × profissional) e ações de favoritar e desfavoritar</t>
+  </si>
+  <si>
+    <t>T22</t>
+  </si>
+  <si>
+    <t>Botão de favoritar no perfil e lista "Minhas favoritas"</t>
+  </si>
+  <si>
+    <t>T23</t>
+  </si>
+  <si>
+    <t>F07</t>
+  </si>
+  <si>
+    <t>Configurar Supabase Storage para armazenar as fotos do portfólio</t>
+  </si>
+  <si>
+    <t>T24</t>
+  </si>
+  <si>
+    <t>Upload de fotos com validação de tipo e tamanho, vinculadas à profissional e ao serviço</t>
+  </si>
+  <si>
+    <t>T25</t>
+  </si>
+  <si>
+    <t>Página pública de portfólio com galeria de fotos e detalhes dos serviços</t>
+  </si>
+  <si>
+    <t>T26</t>
+  </si>
+  <si>
+    <t>F08</t>
+  </si>
+  <si>
+    <t>Criar model BloqueioAgenda (início e fim) e excluir esses períodos do cálculo de horários livres</t>
+  </si>
+  <si>
+    <t>T27</t>
+  </si>
+  <si>
+    <t>Tela para a profissional bloquear e desbloquear horários e dias</t>
+  </si>
+  <si>
+    <t>T28</t>
+  </si>
+  <si>
+    <t>T29</t>
+  </si>
+  <si>
+    <t>Onda 4</t>
+  </si>
+  <si>
+    <t>F09</t>
+  </si>
+  <si>
+    <t>Guardar localização da profissional e da cliente (endereço convertido em coordenadas)</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
+    <t>Busca de profissionais por distância, respeitando o raio definido no perfil</t>
+  </si>
+  <si>
+    <t>Campo de raio de alcance no perfil da profissional e filtro por distância na busca</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>Cadastro de técnicas e vínculo com os serviços</t>
+  </si>
+  <si>
+    <t>Filtro de serviços por técnica na busca</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>Lista de espera por horário desejado, acionada quando um agendamento é cancelado ou recusado</t>
+  </si>
+  <si>
+    <t>Botão "Avise-me se liberar" em horários ocupados e lista de horários desejados</t>
+  </si>
+  <si>
+    <t>Fluxo de status Pendente &gt; Confirmado ou Recusado, alterável só pela profissional dona do agendamento</t>
+  </si>
+  <si>
+    <t>#01</t>
+  </si>
+  <si>
+    <t>#02</t>
+  </si>
+  <si>
+    <t>#03</t>
+  </si>
+  <si>
+    <t>#04</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,33 +466,8 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF333333"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF777777"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF777777"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FF888888"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -416,8 +492,34 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -456,12 +558,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAFAFA"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -492,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -500,57 +621,72 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -560,16 +696,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -872,8 +1007,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:Q34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -884,8 +1019,8 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="28"/>
@@ -896,26 +1031,27 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="23" t="s">
+    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="33" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="28"/>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="28"/>
       <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="36" customHeight="1">
-      <c r="A3" s="24" t="s">
+      <c r="K2" s="23"/>
+    </row>
+    <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="28"/>
@@ -926,7 +1062,7 @@
       <c r="G3" s="28"/>
       <c r="H3" s="28"/>
     </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1">
+    <row r="4" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -952,484 +1088,780 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:17" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+    </row>
+    <row r="6" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
+      <c r="E6" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+    </row>
+    <row r="7" spans="1:17" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="E7" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="J7" s="4"/>
+      <c r="K7" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+    </row>
+    <row r="8" spans="1:17" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="K8" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+    </row>
+    <row r="9" spans="1:17" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="12"/>
+    </row>
+    <row r="10" spans="1:17" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="12"/>
+      <c r="J10" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+    </row>
+    <row r="11" spans="1:17" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="12"/>
+      <c r="J11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+    </row>
+    <row r="12" spans="1:17" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="12"/>
+      <c r="J12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+    </row>
+    <row r="13" spans="1:17" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="12"/>
+      <c r="J13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+    </row>
+    <row r="14" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="1:17" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:17" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="D16" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="E16" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="E17" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="21"/>
+      <c r="H17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="21"/>
+      <c r="H18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="21"/>
+      <c r="H19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="21"/>
+      <c r="H20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="18"/>
+      <c r="H21" s="17"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="18"/>
+      <c r="H22" s="17"/>
+    </row>
+    <row r="23" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="E23" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="18"/>
+      <c r="H23" s="17"/>
+    </row>
+    <row r="24" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="E24" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="18"/>
+      <c r="H24" s="17"/>
+    </row>
+    <row r="25" spans="1:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1">
-      <c r="A9" s="3" t="s">
+      <c r="E25" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+    </row>
+    <row r="26" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+    </row>
+    <row r="27" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="E27" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" s="18"/>
+      <c r="H27" s="17"/>
+    </row>
+    <row r="28" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E28" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="18"/>
+      <c r="H28" s="17"/>
+    </row>
+    <row r="29" spans="1:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="18"/>
+      <c r="H29" s="17"/>
+    </row>
+    <row r="30" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="18"/>
+      <c r="H30" s="17"/>
+    </row>
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F31" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="G31" s="18"/>
+      <c r="H31" s="17"/>
+    </row>
+    <row r="32" spans="1:10" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="s">
+      <c r="E32" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="18"/>
+      <c r="H32" s="17"/>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" spans="1:8" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="18"/>
+      <c r="H33" s="17"/>
+    </row>
+    <row r="34" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1">
-      <c r="A14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1">
-      <c r="A15" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1">
-      <c r="A16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1">
-      <c r="A17" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1">
-      <c r="A18" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.95" customHeight="1">
-      <c r="A19" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.95" customHeight="1">
-      <c r="A22" s="12"/>
-      <c r="B22" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.95" customHeight="1">
-      <c r="A23" s="13"/>
-      <c r="B23" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.95" customHeight="1">
-      <c r="A24" s="14"/>
-      <c r="B24" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-    </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-    </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1">
-      <c r="A28" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-    </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1">
-      <c r="A29" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
+      <c r="E34" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="18"/>
+      <c r="H34" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H18" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="14">
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B29:H29"/>
+  <autoFilter ref="A4:H16" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="13">
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="K13:Q13"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="K12:Q12"/>
+    <mergeCell ref="K7:Q7"/>
+    <mergeCell ref="K6:Q6"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="J5:Q5"/>
+    <mergeCell ref="J10:Q10"/>
     <mergeCell ref="D2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1439,88 +1871,88 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="27.95" customHeight="1">
-      <c r="A1" s="27" t="s">
-        <v>76</v>
+    <row r="1" spans="1:2" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>50</v>
       </c>
       <c r="B1" s="28"/>
     </row>
-    <row r="2" spans="1:2" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="39.950000000000003" customHeight="1">
-      <c r="A5" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="39.950000000000003" customHeight="1">
-      <c r="A6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="39.950000000000003" customHeight="1">
-      <c r="A7" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="39.950000000000003" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="39.950000000000003" customHeight="1">
-      <c r="A9" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="39.950000000000003" customHeight="1">
-      <c r="A10" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>94</v>
+    <row r="2" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\Glowi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FC7DE3-7767-4DDA-B767-8005F2C98474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAC81D1-6CB4-4B46-9C90-85B78FE2E263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="128">
   <si>
     <t>BACKLOG DO PRODUTO — Todas as Ondas até o MVP</t>
   </si>
@@ -421,6 +421,9 @@
   </si>
   <si>
     <t>#04</t>
+  </si>
+  <si>
+    <t>#05</t>
   </si>
 </sst>
 </file>
@@ -1251,8 +1254,12 @@
       <c r="F9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="12"/>
+      <c r="G9" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="10" spans="1:17" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">

--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\Glowi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAC81D1-6CB4-4B46-9C90-85B78FE2E263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36BAE5B-B076-42ED-A881-2D76333AB6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="129">
   <si>
     <t>BACKLOG DO PRODUTO — Todas as Ondas até o MVP</t>
   </si>
@@ -424,6 +424,9 @@
   </si>
   <si>
     <t>#05</t>
+  </si>
+  <si>
+    <t>#06</t>
   </si>
 </sst>
 </file>
@@ -1280,8 +1283,12 @@
       <c r="F10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="12"/>
+      <c r="G10" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="J10" s="32" t="s">
         <v>46</v>
       </c>

--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\Glowi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36BAE5B-B076-42ED-A881-2D76333AB6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503CF489-DA57-47C7-9252-A096340E6C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="INSTRUÇÕES" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BACKLOG!$A$4:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BACKLOG!$A$4:$H$15</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="129">
   <si>
     <t>BACKLOG DO PRODUTO — Todas as Ondas até o MVP</t>
   </si>
@@ -144,9 +144,6 @@
     <t>T10</t>
   </si>
   <si>
-    <t>T11</t>
-  </si>
-  <si>
     <t>F05</t>
   </si>
   <si>
@@ -427,6 +424,9 @@
   </si>
   <si>
     <t>#06</t>
+  </si>
+  <si>
+    <t>Iago</t>
   </si>
 </sst>
 </file>
@@ -619,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -709,6 +709,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1108,19 +1111,19 @@
         <v>28</v>
       </c>
       <c r="E5" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>70</v>
-      </c>
       <c r="H5" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K5" s="28"/>
       <c r="L5" s="28"/>
@@ -1144,20 +1147,20 @@
         <v>17</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>32</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L6" s="28"/>
       <c r="M6" s="28"/>
@@ -1180,20 +1183,20 @@
         <v>19</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L7" s="28"/>
       <c r="M7" s="28"/>
@@ -1216,20 +1219,20 @@
         <v>17</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>32</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L8" s="28"/>
       <c r="M8" s="28"/>
@@ -1252,16 +1255,16 @@
         <v>19</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>32</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -1278,19 +1281,19 @@
         <v>17</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>32</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K10" s="28"/>
       <c r="L10" s="28"/>
@@ -1314,18 +1317,20 @@
         <v>17</v>
       </c>
       <c r="E11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="13"/>
+      <c r="G11" s="13" t="s">
+        <v>128</v>
+      </c>
       <c r="H11" s="12"/>
       <c r="J11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="28"/>
@@ -1348,18 +1353,20 @@
         <v>19</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="13"/>
+      <c r="G12" s="13" t="s">
+        <v>128</v>
+      </c>
       <c r="H12" s="12"/>
       <c r="J12" s="6" t="s">
         <v>11</v>
       </c>
       <c r="K12" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L12" s="28"/>
       <c r="M12" s="28"/>
@@ -1382,18 +1389,20 @@
         <v>19</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" s="13" t="s">
+        <v>128</v>
+      </c>
       <c r="H13" s="12"/>
       <c r="J13" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L13" s="28"/>
       <c r="M13" s="28"/>
@@ -1413,60 +1422,70 @@
         <v>25</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>81</v>
-      </c>
       <c r="F14" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="13"/>
+        <v>36</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>128</v>
+      </c>
       <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:17" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="16"/>
+        <v>16</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>81</v>
+      </c>
       <c r="F15" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:17" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-    </row>
-    <row r="16" spans="1:17" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
+      <c r="G16" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="20"/>
     </row>
     <row r="17" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>30</v>
@@ -1478,7 +1497,7 @@
         <v>19</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>32</v>
@@ -1488,19 +1507,19 @@
     </row>
     <row r="18" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="B18" s="21" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>87</v>
+        <v>17</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>121</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>32</v>
@@ -1516,60 +1535,60 @@
         <v>30</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>122</v>
+        <v>19</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>89</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="20"/>
     </row>
     <row r="20" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="21"/>
-      <c r="H20" s="20"/>
+      <c r="A20" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="18"/>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>40</v>
-      </c>
       <c r="D21" s="18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="18"/>
       <c r="H21" s="17"/>
@@ -1579,38 +1598,38 @@
         <v>88</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G22" s="18"/>
       <c r="H22" s="17"/>
     </row>
     <row r="23" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>32</v>
@@ -1619,42 +1638,42 @@
       <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="18" t="s">
+      <c r="B24" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="17"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
     </row>
     <row r="25" spans="1:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F25" s="25" t="s">
         <v>32</v>
@@ -1663,133 +1682,133 @@
       <c r="H25" s="25"/>
     </row>
     <row r="26" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
+      <c r="A26" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26" s="18"/>
+      <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G27" s="18"/>
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B28" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="18" t="s">
         <v>110</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>111</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>17</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G28" s="18"/>
       <c r="H28" s="17"/>
     </row>
     <row r="29" spans="1:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B29" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>111</v>
-      </c>
       <c r="D29" s="18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="G29" s="18"/>
       <c r="H29" s="17"/>
     </row>
     <row r="30" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G30" s="18"/>
       <c r="H30" s="17"/>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>117</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G31" s="18"/>
       <c r="H31" s="17"/>
@@ -1799,19 +1818,19 @@
         <v>108</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G32" s="18"/>
       <c r="H32" s="17"/>
@@ -1819,50 +1838,29 @@
     </row>
     <row r="33" spans="1:8" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>110</v>
-      </c>
       <c r="C33" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>120</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G33" s="18"/>
       <c r="H33" s="17"/>
     </row>
-    <row r="34" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G34" s="18"/>
-      <c r="H34" s="17"/>
-    </row>
+    <row r="34" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A4:H16" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:H15" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="13">
     <mergeCell ref="K11:Q11"/>
     <mergeCell ref="K8:Q8"/>
@@ -1879,6 +1877,7 @@
     <mergeCell ref="D2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1893,80 +1892,80 @@
   <sheetData>
     <row r="1" spans="1:2" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\Glowi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503CF489-DA57-47C7-9252-A096340E6C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63070E12-99C5-498B-BFAE-3FA629810317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="129">
   <si>
     <t>BACKLOG DO PRODUTO — Todas as Ondas até o MVP</t>
   </si>
@@ -689,6 +689,9 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -709,9 +712,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1029,47 +1029,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="33" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="30" t="s">
+      <c r="E2" s="29"/>
+      <c r="F2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="28"/>
+      <c r="G2" s="29"/>
       <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K2" s="23"/>
     </row>
     <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -1122,16 +1122,16 @@
       <c r="H5" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="J5" s="32" t="s">
+      <c r="J5" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
     </row>
     <row r="6" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
@@ -1159,15 +1159,15 @@
         <v>123</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="27" t="s">
+      <c r="K6" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
     </row>
     <row r="7" spans="1:17" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
@@ -1195,15 +1195,15 @@
         <v>124</v>
       </c>
       <c r="J7" s="4"/>
-      <c r="K7" s="27" t="s">
+      <c r="K7" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
     </row>
     <row r="8" spans="1:17" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
@@ -1231,15 +1231,15 @@
         <v>125</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="27" t="s">
+      <c r="K8" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
     </row>
     <row r="9" spans="1:17" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
@@ -1292,16 +1292,16 @@
       <c r="H10" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="28"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
     </row>
     <row r="11" spans="1:17" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
@@ -1329,15 +1329,15 @@
       <c r="J11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="27" t="s">
+      <c r="K11" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="L11" s="28"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
     </row>
     <row r="12" spans="1:17" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
@@ -1365,15 +1365,15 @@
       <c r="J12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="27" t="s">
+      <c r="K12" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
     </row>
     <row r="13" spans="1:17" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
@@ -1401,15 +1401,15 @@
       <c r="J13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K13" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
     </row>
     <row r="14" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
@@ -1478,7 +1478,7 @@
       <c r="F16" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="27" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="20"/>
@@ -1502,7 +1502,9 @@
       <c r="F17" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="21"/>
+      <c r="G17" s="21" t="s">
+        <v>69</v>
+      </c>
       <c r="H17" s="20"/>
     </row>
     <row r="18" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
@@ -1524,7 +1526,9 @@
       <c r="F18" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="21"/>
+      <c r="G18" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1546,7 +1550,9 @@
       <c r="F19" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="21"/>
+      <c r="G19" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="H19" s="20"/>
     </row>
     <row r="20" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1891,10 +1897,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:2" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
